--- a/output/v7_1/atlas/tablas_regionales.xlsx
+++ b/output/v7_1/atlas/tablas_regionales.xlsx
@@ -27,7 +27,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_La_Rioja" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DC_datos" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DC_calculos" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DC_resumen" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONSTR_v72" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DC_resumen" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -540,6 +541,36 @@
     <comment ref="B2" authorId="0" shapeId="0">
       <text>
         <t>Fuente: output/v7_1/S1/dosis_coste.csv (reproducción de output/v7/R6; Monte Carlo 4.000 extracciones; C4)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment19.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>V7.2</author>
+  </authors>
+  <commentList>
+    <comment ref="C2" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: output/v5_1/T3/tablas/necesidad_provincial.csv (N_anual_central sumada por CCAA, cruce por código INE)</t>
+      </text>
+    </comment>
+    <comment ref="D2" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: data/processed/v7/panel_ccaa_q_v7.csv (visados, Ministerio), suma de 2025</t>
+      </text>
+    </comment>
+    <comment ref="E2" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: data/processed/v7/panel_ccaa_q_v7.csv (visados, Ministerio), máximo anual 2007-2025</t>
+      </text>
+    </comment>
+    <comment ref="I2" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: output/v7_2/construccion/impactos_construccion.csv (Monte Carlo, 4.000 extracciones, rejilla)</t>
       </text>
     </comment>
   </commentList>
@@ -1901,7 +1932,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>RMSE base exigente ×100</t>
+          <t>RMSE base más exigente ×100</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1911,7 +1942,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>¿Bate?</t>
+          <t>¿Bate a la base más exigente?</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2409,7 +2440,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>RMSE base exigente ×100</t>
+          <t>RMSE base más exigente ×100</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2419,7 +2450,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>¿Bate?</t>
+          <t>¿Bate a la base más exigente?</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2917,7 +2948,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>RMSE base exigente ×100</t>
+          <t>RMSE base más exigente ×100</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2927,7 +2958,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>¿Bate?</t>
+          <t>¿Bate a la base más exigente?</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3425,7 +3456,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>RMSE base exigente ×100</t>
+          <t>RMSE base más exigente ×100</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3435,7 +3466,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>¿Bate?</t>
+          <t>¿Bate a la base más exigente?</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3933,7 +3964,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>RMSE base exigente ×100</t>
+          <t>RMSE base más exigente ×100</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3943,7 +3974,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>¿Bate?</t>
+          <t>¿Bate a la base más exigente?</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4441,7 +4472,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>RMSE base exigente ×100</t>
+          <t>RMSE base más exigente ×100</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4451,7 +4482,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>¿Bate?</t>
+          <t>¿Bate a la base más exigente?</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4949,7 +4980,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>RMSE base exigente ×100</t>
+          <t>RMSE base más exigente ×100</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4959,7 +4990,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>¿Bate?</t>
+          <t>¿Bate a la base más exigente?</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5457,7 +5488,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>RMSE base exigente ×100</t>
+          <t>RMSE base más exigente ×100</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5467,7 +5498,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>¿Bate?</t>
+          <t>¿Bate a la base más exigente?</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5965,7 +5996,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>RMSE base exigente ×100</t>
+          <t>RMSE base más exigente ×100</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5975,7 +6006,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>¿Bate?</t>
+          <t>¿Bate a la base más exigente?</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6285,18 +6316,20 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0</v>
+        <v>75616.00750000001</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0</v>
+        <v>-0.9232</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0</v>
+        <v>-0.9232</v>
       </c>
       <c r="H3" s="5" t="n"/>
       <c r="I3" s="5" t="n"/>
       <c r="J3" s="5" t="n"/>
-      <c r="K3" s="5" t="n"/>
+      <c r="K3" s="5" t="n">
+        <v>-0.1244</v>
+      </c>
       <c r="L3" s="5" t="n"/>
       <c r="M3" s="5" t="n"/>
       <c r="N3" s="5" t="inlineStr">
@@ -6327,18 +6360,20 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>75616.00750000001</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0</v>
+        <v>-0.8172</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0</v>
+        <v>-0.8172</v>
       </c>
       <c r="H4" s="5" t="n"/>
       <c r="I4" s="5" t="n"/>
       <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="n"/>
+      <c r="K4" s="5" t="n">
+        <v>-0.108</v>
+      </c>
       <c r="L4" s="5" t="n"/>
       <c r="M4" s="5" t="n"/>
       <c r="N4" s="5" t="inlineStr">
@@ -6770,7 +6805,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -6812,7 +6847,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -6873,18 +6908,20 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>31598.8797</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0</v>
+        <v>-2.1901</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0</v>
+        <v>-2.1901</v>
       </c>
       <c r="H16" s="5" t="n"/>
       <c r="I16" s="5" t="n"/>
       <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="n"/>
+      <c r="K16" s="5" t="n">
+        <v>-0.6961000000000001</v>
+      </c>
       <c r="L16" s="5" t="n"/>
       <c r="M16" s="5" t="n"/>
       <c r="N16" s="5" t="inlineStr">
@@ -6915,18 +6952,20 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0</v>
+        <v>31598.8797</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0</v>
+        <v>-1.9596</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0</v>
+        <v>-1.9596</v>
       </c>
       <c r="H17" s="5" t="n"/>
       <c r="I17" s="5" t="n"/>
       <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="n"/>
+      <c r="K17" s="5" t="n">
+        <v>-0.6143999999999999</v>
+      </c>
       <c r="L17" s="5" t="n"/>
       <c r="M17" s="5" t="n"/>
       <c r="N17" s="5" t="inlineStr">
@@ -7358,7 +7397,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -7400,7 +7439,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -7461,18 +7500,20 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0</v>
+        <v>10814.0056</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0</v>
+        <v>-0.8932</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0</v>
+        <v>-0.8932</v>
       </c>
       <c r="H29" s="5" t="n"/>
       <c r="I29" s="5" t="n"/>
       <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="n"/>
+      <c r="K29" s="5" t="n">
+        <v>-0.843</v>
+      </c>
       <c r="L29" s="5" t="n"/>
       <c r="M29" s="5" t="n"/>
       <c r="N29" s="5" t="inlineStr">
@@ -7503,18 +7544,20 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0</v>
+        <v>10814.0056</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0</v>
+        <v>-0.8017</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0</v>
+        <v>-0.8017</v>
       </c>
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="5" t="n"/>
       <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="n"/>
+      <c r="K30" s="5" t="n">
+        <v>-0.7372</v>
+      </c>
       <c r="L30" s="5" t="n"/>
       <c r="M30" s="5" t="n"/>
       <c r="N30" s="5" t="inlineStr">
@@ -7946,7 +7989,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -7988,7 +8031,7 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -8049,18 +8092,20 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0</v>
+        <v>11278.4873</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0</v>
+        <v>-0.9575</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0</v>
+        <v>-0.9575</v>
       </c>
       <c r="H42" s="5" t="n"/>
       <c r="I42" s="5" t="n"/>
       <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="n"/>
+      <c r="K42" s="5" t="n">
+        <v>-0.8669</v>
+      </c>
       <c r="L42" s="5" t="n"/>
       <c r="M42" s="5" t="n"/>
       <c r="N42" s="5" t="inlineStr">
@@ -8091,18 +8136,20 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0</v>
+        <v>11278.4873</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0</v>
+        <v>-0.8598</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0</v>
+        <v>-0.8598</v>
       </c>
       <c r="H43" s="5" t="n"/>
       <c r="I43" s="5" t="n"/>
       <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="n"/>
+      <c r="K43" s="5" t="n">
+        <v>-0.7582</v>
+      </c>
       <c r="L43" s="5" t="n"/>
       <c r="M43" s="5" t="n"/>
       <c r="N43" s="5" t="inlineStr">
@@ -8534,7 +8581,7 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -8576,7 +8623,7 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -8637,18 +8684,20 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0</v>
+        <v>61641.3455</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>0</v>
+        <v>-4.2445</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0</v>
+        <v>-4.2445</v>
       </c>
       <c r="H55" s="5" t="n"/>
       <c r="I55" s="5" t="n"/>
       <c r="J55" s="5" t="n"/>
-      <c r="K55" s="5" t="n"/>
+      <c r="K55" s="5" t="n">
+        <v>-0.7026</v>
+      </c>
       <c r="L55" s="5" t="n"/>
       <c r="M55" s="5" t="n"/>
       <c r="N55" s="5" t="inlineStr">
@@ -8679,18 +8728,20 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0</v>
+        <v>61641.3455</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0</v>
+        <v>-3.777</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0</v>
+        <v>-3.777</v>
       </c>
       <c r="H56" s="5" t="n"/>
       <c r="I56" s="5" t="n"/>
       <c r="J56" s="5" t="n"/>
-      <c r="K56" s="5" t="n"/>
+      <c r="K56" s="5" t="n">
+        <v>-0.609</v>
+      </c>
       <c r="L56" s="5" t="n"/>
       <c r="M56" s="5" t="n"/>
       <c r="N56" s="5" t="inlineStr">
@@ -9122,7 +9173,7 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -9164,7 +9215,7 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -9225,13 +9276,13 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>430.4746</v>
+        <v>13694.4719</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>-0.0625</v>
+        <v>-1.9869</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>-0.0625</v>
+        <v>-1.9869</v>
       </c>
       <c r="H68" s="5" t="n"/>
       <c r="I68" s="5" t="n"/>
@@ -9269,13 +9320,13 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>430.4746</v>
+        <v>13694.4719</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>-0.0559</v>
+        <v>-1.7783</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>-0.0559</v>
+        <v>-1.7783</v>
       </c>
       <c r="H69" s="5" t="n"/>
       <c r="I69" s="5" t="n"/>
@@ -9714,7 +9765,7 @@
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -9756,7 +9807,7 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -9817,18 +9868,20 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>0</v>
+        <v>20772.273</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>0</v>
+        <v>-0.7196</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0</v>
+        <v>-0.7196</v>
       </c>
       <c r="H81" s="5" t="n"/>
       <c r="I81" s="5" t="n"/>
       <c r="J81" s="5" t="n"/>
-      <c r="K81" s="5" t="n"/>
+      <c r="K81" s="5" t="n">
+        <v>-0.3536</v>
+      </c>
       <c r="L81" s="5" t="n"/>
       <c r="M81" s="5" t="n"/>
       <c r="N81" s="5" t="inlineStr">
@@ -9859,18 +9912,20 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0</v>
+        <v>20772.273</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>0</v>
+        <v>-0.6399</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0</v>
+        <v>-0.6399</v>
       </c>
       <c r="H82" s="5" t="n"/>
       <c r="I82" s="5" t="n"/>
       <c r="J82" s="5" t="n"/>
-      <c r="K82" s="5" t="n"/>
+      <c r="K82" s="5" t="n">
+        <v>-0.3077</v>
+      </c>
       <c r="L82" s="5" t="n"/>
       <c r="M82" s="5" t="n"/>
       <c r="N82" s="5" t="inlineStr">
@@ -10302,7 +10357,7 @@
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -10344,7 +10399,7 @@
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
@@ -10405,18 +10460,20 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0</v>
+        <v>70257.7784</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0</v>
+        <v>-3.0827</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0</v>
+        <v>-3.0827</v>
       </c>
       <c r="H94" s="5" t="n"/>
       <c r="I94" s="5" t="n"/>
       <c r="J94" s="5" t="n"/>
-      <c r="K94" s="5" t="n"/>
+      <c r="K94" s="5" t="n">
+        <v>-0.4504</v>
+      </c>
       <c r="L94" s="5" t="n"/>
       <c r="M94" s="5" t="n"/>
       <c r="N94" s="5" t="inlineStr">
@@ -10447,18 +10504,20 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>0</v>
+        <v>70257.7784</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>0</v>
+        <v>-2.7627</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0</v>
+        <v>-2.7627</v>
       </c>
       <c r="H95" s="5" t="n"/>
       <c r="I95" s="5" t="n"/>
       <c r="J95" s="5" t="n"/>
-      <c r="K95" s="5" t="n"/>
+      <c r="K95" s="5" t="n">
+        <v>-0.3927</v>
+      </c>
       <c r="L95" s="5" t="n"/>
       <c r="M95" s="5" t="n"/>
       <c r="N95" s="5" t="inlineStr">
@@ -10890,7 +10949,7 @@
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
@@ -10932,7 +10991,7 @@
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
@@ -10993,13 +11052,13 @@
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>9200.879999999999</v>
+        <v>97413.1351</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>-0.1314</v>
+        <v>-1.3915</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>-0.1314</v>
+        <v>-1.3915</v>
       </c>
       <c r="H107" s="5" t="n"/>
       <c r="I107" s="5" t="n"/>
@@ -11037,13 +11096,13 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>9200.879999999999</v>
+        <v>97413.1351</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>-0.1175</v>
+        <v>-1.2443</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>-0.1175</v>
+        <v>-1.2443</v>
       </c>
       <c r="H108" s="5" t="n"/>
       <c r="I108" s="5" t="n"/>
@@ -11482,7 +11541,7 @@
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
@@ -11524,7 +11583,7 @@
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
@@ -11585,18 +11644,20 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>0</v>
+        <v>98684.787</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>0</v>
+        <v>-2.1275</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0</v>
+        <v>-2.1275</v>
       </c>
       <c r="H120" s="5" t="n"/>
       <c r="I120" s="5" t="n"/>
       <c r="J120" s="5" t="n"/>
-      <c r="K120" s="5" t="n"/>
+      <c r="K120" s="5" t="n">
+        <v>-0.2188</v>
+      </c>
       <c r="L120" s="5" t="n"/>
       <c r="M120" s="5" t="n"/>
       <c r="N120" s="5" t="inlineStr">
@@ -11627,18 +11688,20 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>0</v>
+        <v>98684.787</v>
       </c>
       <c r="F121" s="5" t="n">
-        <v>0</v>
+        <v>-1.8774</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0</v>
+        <v>-1.8774</v>
       </c>
       <c r="H121" s="5" t="n"/>
       <c r="I121" s="5" t="n"/>
       <c r="J121" s="5" t="n"/>
-      <c r="K121" s="5" t="n"/>
+      <c r="K121" s="5" t="n">
+        <v>-0.1907</v>
+      </c>
       <c r="L121" s="5" t="n"/>
       <c r="M121" s="5" t="n"/>
       <c r="N121" s="5" t="inlineStr">
@@ -12070,7 +12133,7 @@
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
@@ -12112,7 +12175,7 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
@@ -12173,18 +12236,20 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>0</v>
+        <v>8087.8817</v>
       </c>
       <c r="F133" s="5" t="n">
-        <v>0</v>
+        <v>-1.2155</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0</v>
+        <v>-1.2155</v>
       </c>
       <c r="H133" s="5" t="n"/>
       <c r="I133" s="5" t="n"/>
       <c r="J133" s="5" t="n"/>
-      <c r="K133" s="5" t="n"/>
+      <c r="K133" s="5" t="n">
+        <v>-1.5185</v>
+      </c>
       <c r="L133" s="5" t="n"/>
       <c r="M133" s="5" t="n"/>
       <c r="N133" s="5" t="inlineStr">
@@ -12215,18 +12280,20 @@
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>0</v>
+        <v>8087.8817</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>0</v>
+        <v>-1.0648</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0</v>
+        <v>-1.0648</v>
       </c>
       <c r="H134" s="5" t="n"/>
       <c r="I134" s="5" t="n"/>
       <c r="J134" s="5" t="n"/>
-      <c r="K134" s="5" t="n"/>
+      <c r="K134" s="5" t="n">
+        <v>-1.3246</v>
+      </c>
       <c r="L134" s="5" t="n"/>
       <c r="M134" s="5" t="n"/>
       <c r="N134" s="5" t="inlineStr">
@@ -12658,7 +12725,7 @@
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
@@ -12700,7 +12767,7 @@
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
@@ -12761,18 +12828,20 @@
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>0</v>
+        <v>24862.8822</v>
       </c>
       <c r="F146" s="5" t="n">
-        <v>0</v>
+        <v>-0.9018</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0</v>
+        <v>-0.9018</v>
       </c>
       <c r="H146" s="5" t="n"/>
       <c r="I146" s="5" t="n"/>
       <c r="J146" s="5" t="n"/>
-      <c r="K146" s="5" t="n"/>
+      <c r="K146" s="5" t="n">
+        <v>-0.3782</v>
+      </c>
       <c r="L146" s="5" t="n"/>
       <c r="M146" s="5" t="n"/>
       <c r="N146" s="5" t="inlineStr">
@@ -12803,18 +12872,20 @@
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>0</v>
+        <v>24862.8822</v>
       </c>
       <c r="F147" s="5" t="n">
-        <v>0</v>
+        <v>-0.8109</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0</v>
+        <v>-0.8109</v>
       </c>
       <c r="H147" s="5" t="n"/>
       <c r="I147" s="5" t="n"/>
       <c r="J147" s="5" t="n"/>
-      <c r="K147" s="5" t="n"/>
+      <c r="K147" s="5" t="n">
+        <v>-0.3284</v>
+      </c>
       <c r="L147" s="5" t="n"/>
       <c r="M147" s="5" t="n"/>
       <c r="N147" s="5" t="inlineStr">
@@ -13246,7 +13317,7 @@
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
@@ -13288,7 +13359,7 @@
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
@@ -13838,7 +13909,7 @@
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
@@ -13880,7 +13951,7 @@
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
@@ -13941,18 +14012,20 @@
         </is>
       </c>
       <c r="E172" s="5" t="n">
-        <v>0</v>
+        <v>66427.36139999999</v>
       </c>
       <c r="F172" s="5" t="n">
-        <v>0</v>
+        <v>-4.3958</v>
       </c>
       <c r="G172" s="5" t="n">
-        <v>0</v>
+        <v>-4.3958</v>
       </c>
       <c r="H172" s="5" t="n"/>
       <c r="I172" s="5" t="n"/>
       <c r="J172" s="5" t="n"/>
-      <c r="K172" s="5" t="n"/>
+      <c r="K172" s="5" t="n">
+        <v>-0.6735</v>
+      </c>
       <c r="L172" s="5" t="n"/>
       <c r="M172" s="5" t="n"/>
       <c r="N172" s="5" t="inlineStr">
@@ -13983,18 +14056,20 @@
         </is>
       </c>
       <c r="E173" s="5" t="n">
-        <v>0</v>
+        <v>66427.36139999999</v>
       </c>
       <c r="F173" s="5" t="n">
-        <v>0</v>
+        <v>-3.9586</v>
       </c>
       <c r="G173" s="5" t="n">
-        <v>0</v>
+        <v>-3.9586</v>
       </c>
       <c r="H173" s="5" t="n"/>
       <c r="I173" s="5" t="n"/>
       <c r="J173" s="5" t="n"/>
-      <c r="K173" s="5" t="n"/>
+      <c r="K173" s="5" t="n">
+        <v>-0.5924</v>
+      </c>
       <c r="L173" s="5" t="n"/>
       <c r="M173" s="5" t="n"/>
       <c r="N173" s="5" t="inlineStr">
@@ -14426,7 +14501,7 @@
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
@@ -14468,7 +14543,7 @@
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
@@ -14529,13 +14604,13 @@
         </is>
       </c>
       <c r="E185" s="5" t="n">
-        <v>9092.5062</v>
+        <v>9483.436799999999</v>
       </c>
       <c r="F185" s="5" t="n">
-        <v>-1.517</v>
+        <v>-1.5822</v>
       </c>
       <c r="G185" s="5" t="n">
-        <v>-1.517</v>
+        <v>-1.5822</v>
       </c>
       <c r="H185" s="5" t="n"/>
       <c r="I185" s="5" t="n"/>
@@ -14573,13 +14648,13 @@
         </is>
       </c>
       <c r="E186" s="5" t="n">
-        <v>9092.5062</v>
+        <v>9483.436799999999</v>
       </c>
       <c r="F186" s="5" t="n">
-        <v>-1.3764</v>
+        <v>-1.4356</v>
       </c>
       <c r="G186" s="5" t="n">
-        <v>-1.3764</v>
+        <v>-1.4356</v>
       </c>
       <c r="H186" s="5" t="n"/>
       <c r="I186" s="5" t="n"/>
@@ -15018,7 +15093,7 @@
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D196" s="5" t="inlineStr">
@@ -15060,7 +15135,7 @@
       </c>
       <c r="C197" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D197" s="5" t="inlineStr">
@@ -15121,13 +15196,13 @@
         </is>
       </c>
       <c r="E198" s="5" t="n">
-        <v>10427.3345</v>
+        <v>21145.2557</v>
       </c>
       <c r="F198" s="5" t="n">
-        <v>-0.9282</v>
+        <v>-1.8823</v>
       </c>
       <c r="G198" s="5" t="n">
-        <v>-0.9282</v>
+        <v>-1.8823</v>
       </c>
       <c r="H198" s="5" t="n"/>
       <c r="I198" s="5" t="n"/>
@@ -15165,13 +15240,13 @@
         </is>
       </c>
       <c r="E199" s="5" t="n">
-        <v>10427.3345</v>
+        <v>21145.2557</v>
       </c>
       <c r="F199" s="5" t="n">
-        <v>-0.8232</v>
+        <v>-1.6694</v>
       </c>
       <c r="G199" s="5" t="n">
-        <v>-0.8232</v>
+        <v>-1.6694</v>
       </c>
       <c r="H199" s="5" t="n"/>
       <c r="I199" s="5" t="n"/>
@@ -15610,7 +15685,7 @@
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D209" s="5" t="inlineStr">
@@ -15652,7 +15727,7 @@
       </c>
       <c r="C210" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D210" s="5" t="inlineStr">
@@ -15713,18 +15788,20 @@
         </is>
       </c>
       <c r="E211" s="5" t="n">
-        <v>0</v>
+        <v>7039.6705</v>
       </c>
       <c r="F211" s="5" t="n">
-        <v>0</v>
+        <v>-1.8697</v>
       </c>
       <c r="G211" s="5" t="n">
-        <v>0</v>
+        <v>-1.8697</v>
       </c>
       <c r="H211" s="5" t="n"/>
       <c r="I211" s="5" t="n"/>
       <c r="J211" s="5" t="n"/>
-      <c r="K211" s="5" t="n"/>
+      <c r="K211" s="5" t="n">
+        <v>-2.7401</v>
+      </c>
       <c r="L211" s="5" t="n"/>
       <c r="M211" s="5" t="n"/>
       <c r="N211" s="5" t="inlineStr">
@@ -15755,18 +15832,20 @@
         </is>
       </c>
       <c r="E212" s="5" t="n">
-        <v>0</v>
+        <v>7039.6705</v>
       </c>
       <c r="F212" s="5" t="n">
-        <v>0</v>
+        <v>-1.6652</v>
       </c>
       <c r="G212" s="5" t="n">
-        <v>0</v>
+        <v>-1.6652</v>
       </c>
       <c r="H212" s="5" t="n"/>
       <c r="I212" s="5" t="n"/>
       <c r="J212" s="5" t="n"/>
-      <c r="K212" s="5" t="n"/>
+      <c r="K212" s="5" t="n">
+        <v>-2.3526</v>
+      </c>
       <c r="L212" s="5" t="n"/>
       <c r="M212" s="5" t="n"/>
       <c r="N212" s="5" t="inlineStr">
@@ -16198,7 +16277,7 @@
       </c>
       <c r="C222" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D222" s="5" t="inlineStr">
@@ -16240,7 +16319,7 @@
       </c>
       <c r="C223" s="5" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="D223" s="5" t="inlineStr">
@@ -16590,7 +16669,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>RMSE base exigente ×100</t>
+          <t>RMSE base más exigente ×100</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16600,7 +16679,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>¿Bate?</t>
+          <t>¿Bate a la base más exigente?</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -24604,6 +24683,802 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Construcción adicional con dosis no nula (v7.2, C4). Entradas en azul (fuente en la nota), cálculos en negro, vínculos en verde.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CCAA (código INE)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CCAA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Necesidad anual T3 (viv./año)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Visados 2025</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Máx. anual de visados 2007-2025</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Capacidad observada</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Dosis anual máxima</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Dosis anual mínima (50 %)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Δ precio de compra 10 años, mediana (%)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Robusto</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>40815</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>27454</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>38693</v>
+      </c>
+      <c r="F3" s="7">
+        <f>MAX(E3-D3,0)</f>
+        <v/>
+      </c>
+      <c r="G3" s="7">
+        <f>MIN(C3,F3)</f>
+        <v/>
+      </c>
+      <c r="H3" s="7">
+        <f>0.5*G3</f>
+        <v/>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>-0.8172</v>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Aragón</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>5405</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>4031</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>8754</v>
+      </c>
+      <c r="F4" s="7">
+        <f>MAX(E4-D4,0)</f>
+        <v/>
+      </c>
+      <c r="G4" s="7">
+        <f>MIN(C4,F4)</f>
+        <v/>
+      </c>
+      <c r="H4" s="7">
+        <f>0.5*G4</f>
+        <v/>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>-1.9596</v>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Asturias</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>1612</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>3096</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>6155</v>
+      </c>
+      <c r="F5" s="7">
+        <f>MAX(E5-D5,0)</f>
+        <v/>
+      </c>
+      <c r="G5" s="7">
+        <f>MIN(C5,F5)</f>
+        <v/>
+      </c>
+      <c r="H5" s="7">
+        <f>0.5*G5</f>
+        <v/>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>-0.8017</v>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Illes Balears</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>7358</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4215</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>5886</v>
+      </c>
+      <c r="F6" s="7">
+        <f>MAX(E6-D6,0)</f>
+        <v/>
+      </c>
+      <c r="G6" s="7">
+        <f>MIN(C6,F6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="7">
+        <f>0.5*G6</f>
+        <v/>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>-0.8598</v>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Canarias</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>10750</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>4666</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>13751</v>
+      </c>
+      <c r="F7" s="7">
+        <f>MAX(E7-D7,0)</f>
+        <v/>
+      </c>
+      <c r="G7" s="7">
+        <f>MIN(C7,F7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="7">
+        <f>0.5*G7</f>
+        <v/>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>-3.777</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>2036</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1505</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>4083</v>
+      </c>
+      <c r="F8" s="7">
+        <f>MAX(E8-D8,0)</f>
+        <v/>
+      </c>
+      <c r="G8" s="7">
+        <f>MIN(C8,F8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="7">
+        <f>0.5*G8</f>
+        <v/>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>-1.7783</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3101</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>6567</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>17250</v>
+      </c>
+      <c r="F9" s="7">
+        <f>MAX(E9-D9,0)</f>
+        <v/>
+      </c>
+      <c r="G9" s="7">
+        <f>MIN(C9,F9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="7">
+        <f>0.5*G9</f>
+        <v/>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>-0.6399</v>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>10421</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>6473</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>24123</v>
+      </c>
+      <c r="F10" s="7">
+        <f>MAX(E10-D10,0)</f>
+        <v/>
+      </c>
+      <c r="G10" s="7">
+        <f>MIN(C10,F10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="7">
+        <f>0.5*G10</f>
+        <v/>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>-2.7627</v>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>47024</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>13882</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>28302</v>
+      </c>
+      <c r="F11" s="7">
+        <f>MAX(E11-D11,0)</f>
+        <v/>
+      </c>
+      <c r="G11" s="7">
+        <f>MIN(C11,F11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="7">
+        <f>0.5*G11</f>
+        <v/>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>-1.2443</v>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Comunitat Valenciana</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>39793</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>14256</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>28847</v>
+      </c>
+      <c r="F12" s="7">
+        <f>MAX(E12-D12,0)</f>
+        <v/>
+      </c>
+      <c r="G12" s="7">
+        <f>MIN(C12,F12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="7">
+        <f>0.5*G12</f>
+        <v/>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>-1.8774</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Extremadura</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1204</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>2362</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>5748</v>
+      </c>
+      <c r="F13" s="7">
+        <f>MAX(E13-D13,0)</f>
+        <v/>
+      </c>
+      <c r="G13" s="7">
+        <f>MIN(C13,F13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="7">
+        <f>0.5*G13</f>
+        <v/>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>-1.0648</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>3661</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>4894</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>16735</v>
+      </c>
+      <c r="F14" s="7">
+        <f>MAX(E14-D14,0)</f>
+        <v/>
+      </c>
+      <c r="G14" s="7">
+        <f>MIN(C14,F14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="7">
+        <f>0.5*G14</f>
+        <v/>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>-0.8109</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>45980</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>17718</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>20605</v>
+      </c>
+      <c r="F15" s="7">
+        <f>MAX(E15-D15,0)</f>
+        <v/>
+      </c>
+      <c r="G15" s="7">
+        <f>MIN(C15,F15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="7">
+        <f>0.5*G15</f>
+        <v/>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>-0.3309</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Región de Murcia</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>12599</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>4308</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>14198</v>
+      </c>
+      <c r="F16" s="7">
+        <f>MAX(E16-D16,0)</f>
+        <v/>
+      </c>
+      <c r="G16" s="7">
+        <f>MIN(C16,F16)</f>
+        <v/>
+      </c>
+      <c r="H16" s="7">
+        <f>0.5*G16</f>
+        <v/>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>-3.9586</v>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Comunidad Foral de Navarra</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>3565</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1765</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>3172</v>
+      </c>
+      <c r="F17" s="7">
+        <f>MAX(E17-D17,0)</f>
+        <v/>
+      </c>
+      <c r="G17" s="7">
+        <f>MIN(C17,F17)</f>
+        <v/>
+      </c>
+      <c r="H17" s="7">
+        <f>0.5*G17</f>
+        <v/>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>-1.4356</v>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>País Vasco</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>8237</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3073</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>6202</v>
+      </c>
+      <c r="F18" s="7">
+        <f>MAX(E18-D18,0)</f>
+        <v/>
+      </c>
+      <c r="G18" s="7">
+        <f>MIN(C18,F18)</f>
+        <v/>
+      </c>
+      <c r="H18" s="7">
+        <f>0.5*G18</f>
+        <v/>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>-1.6694</v>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>La Rioja</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1602</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1405</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>2449</v>
+      </c>
+      <c r="F19" s="7">
+        <f>MAX(E19-D19,0)</f>
+        <v/>
+      </c>
+      <c r="G19" s="7">
+        <f>MIN(C19,F19)</f>
+        <v/>
+      </c>
+      <c r="H19" s="7">
+        <f>0.5*G19</f>
+        <v/>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>-1.6652</v>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Enlace a la mediana de DC_datos (construcción adicional, compra, Andalucía):</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" s="6">
+        <f>DC_datos!F4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>La rebaja de impuestos y costes de construcción es NO DIFUNDIBLE por sobrestimación de diseño (v7.2); sus filas de DC_datos se conservan solo para trazabilidad.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -24910,7 +25785,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -24919,30 +25794,30 @@
         </is>
       </c>
       <c r="C11" s="7">
-        <f t="array" ref="C11">IFERROR(MEDIAN(IF((DC_datos!C3:C223="rebaja de impuestos y costes de construcción")*(DC_datos!D3:D223="compra")*ISNUMBER(DC_datos!E3:E223),DC_datos!E3:E223)),"—")</f>
+        <f t="array" ref="C11">IFERROR(MEDIAN(IF((DC_datos!C3:C223="rebaja de impuestos y costes de construcción (no difundible)")*(DC_datos!D3:D223="compra")*ISNUMBER(DC_datos!E3:E223),DC_datos!E3:E223)),"—")</f>
         <v/>
       </c>
       <c r="D11" s="7">
-        <f t="array" ref="D11">IFERROR(MEDIAN(IF((DC_datos!C3:C223="rebaja de impuestos y costes de construcción")*(DC_datos!D3:D223="compra")*ISNUMBER(DC_datos!F3:F223),DC_datos!F3:F223)),"—")</f>
+        <f t="array" ref="D11">IFERROR(MEDIAN(IF((DC_datos!C3:C223="rebaja de impuestos y costes de construcción (no difundible)")*(DC_datos!D3:D223="compra")*ISNUMBER(DC_datos!F3:F223),DC_datos!F3:F223)),"—")</f>
         <v/>
       </c>
       <c r="E11" s="7">
-        <f t="array" ref="E11">IFERROR(MEDIAN(IF((DC_datos!C3:C223="rebaja de impuestos y costes de construcción")*(DC_datos!D3:D223="compra")*ISNUMBER(DC_datos!H3:H223),DC_datos!H3:H223)),"—")</f>
+        <f t="array" ref="E11">IFERROR(MEDIAN(IF((DC_datos!C3:C223="rebaja de impuestos y costes de construcción (no difundible)")*(DC_datos!D3:D223="compra")*ISNUMBER(DC_datos!H3:H223),DC_datos!H3:H223)),"—")</f>
         <v/>
       </c>
       <c r="F11" s="7">
-        <f t="array" ref="F11">IFERROR(MEDIAN(IF((DC_datos!C3:C223="rebaja de impuestos y costes de construcción")*(DC_datos!D3:D223="compra")*ISNUMBER(DC_datos!K3:K223),DC_datos!K3:K223)),"—")</f>
+        <f t="array" ref="F11">IFERROR(MEDIAN(IF((DC_datos!C3:C223="rebaja de impuestos y costes de construcción (no difundible)")*(DC_datos!D3:D223="compra")*ISNUMBER(DC_datos!K3:K223),DC_datos!K3:K223)),"—")</f>
         <v/>
       </c>
       <c r="G11" s="7">
-        <f t="array" ref="G11">IFERROR(MEDIAN(IF((DC_datos!C3:C223="rebaja de impuestos y costes de construcción")*(DC_datos!D3:D223="compra")*ISNUMBER(DC_datos!L3:L223),DC_datos!L3:L223)),"—")</f>
+        <f t="array" ref="G11">IFERROR(MEDIAN(IF((DC_datos!C3:C223="rebaja de impuestos y costes de construcción (no difundible)")*(DC_datos!D3:D223="compra")*ISNUMBER(DC_datos!L3:L223),DC_datos!L3:L223)),"—")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>rebaja de impuestos y costes de construcción</t>
+          <t>rebaja de impuestos y costes de construcción (no difundible)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -24951,23 +25826,23 @@
         </is>
       </c>
       <c r="C12" s="7">
-        <f t="array" ref="C12">IFERROR(MEDIAN(IF((DC_datos!C3:C223="rebaja de impuestos y costes de construcción")*(DC_datos!D3:D223="alquiler")*ISNUMBER(DC_datos!E3:E223),DC_datos!E3:E223)),"—")</f>
+        <f t="array" ref="C12">IFERROR(MEDIAN(IF((DC_datos!C3:C223="rebaja de impuestos y costes de construcción (no difundible)")*(DC_datos!D3:D223="alquiler")*ISNUMBER(DC_datos!E3:E223),DC_datos!E3:E223)),"—")</f>
         <v/>
       </c>
       <c r="D12" s="7">
-        <f t="array" ref="D12">IFERROR(MEDIAN(IF((DC_datos!C3:C223="rebaja de impuestos y costes de construcción")*(DC_datos!D3:D223="alquiler")*ISNUMBER(DC_datos!F3:F223),DC_datos!F3:F223)),"—")</f>
+        <f t="array" ref="D12">IFERROR(MEDIAN(IF((DC_datos!C3:C223="rebaja de impuestos y costes de construcción (no difundible)")*(DC_datos!D3:D223="alquiler")*ISNUMBER(DC_datos!F3:F223),DC_datos!F3:F223)),"—")</f>
         <v/>
       </c>
       <c r="E12" s="7">
-        <f t="array" ref="E12">IFERROR(MEDIAN(IF((DC_datos!C3:C223="rebaja de impuestos y costes de construcción")*(DC_datos!D3:D223="alquiler")*ISNUMBER(DC_datos!H3:H223),DC_datos!H3:H223)),"—")</f>
+        <f t="array" ref="E12">IFERROR(MEDIAN(IF((DC_datos!C3:C223="rebaja de impuestos y costes de construcción (no difundible)")*(DC_datos!D3:D223="alquiler")*ISNUMBER(DC_datos!H3:H223),DC_datos!H3:H223)),"—")</f>
         <v/>
       </c>
       <c r="F12" s="7">
-        <f t="array" ref="F12">IFERROR(MEDIAN(IF((DC_datos!C3:C223="rebaja de impuestos y costes de construcción")*(DC_datos!D3:D223="alquiler")*ISNUMBER(DC_datos!K3:K223),DC_datos!K3:K223)),"—")</f>
+        <f t="array" ref="F12">IFERROR(MEDIAN(IF((DC_datos!C3:C223="rebaja de impuestos y costes de construcción (no difundible)")*(DC_datos!D3:D223="alquiler")*ISNUMBER(DC_datos!K3:K223),DC_datos!K3:K223)),"—")</f>
         <v/>
       </c>
       <c r="G12" s="7">
-        <f t="array" ref="G12">IFERROR(MEDIAN(IF((DC_datos!C3:C223="rebaja de impuestos y costes de construcción")*(DC_datos!D3:D223="alquiler")*ISNUMBER(DC_datos!L3:L223),DC_datos!L3:L223)),"—")</f>
+        <f t="array" ref="G12">IFERROR(MEDIAN(IF((DC_datos!C3:C223="rebaja de impuestos y costes de construcción (no difundible)")*(DC_datos!D3:D223="alquiler")*ISNUMBER(DC_datos!L3:L223),DC_datos!L3:L223)),"—")</f>
         <v/>
       </c>
     </row>
@@ -25377,7 +26252,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>RMSE base exigente ×100</t>
+          <t>RMSE base más exigente ×100</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -25387,7 +26262,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>¿Bate?</t>
+          <t>¿Bate a la base más exigente?</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -25885,7 +26760,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>RMSE base exigente ×100</t>
+          <t>RMSE base más exigente ×100</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -25895,7 +26770,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>¿Bate?</t>
+          <t>¿Bate a la base más exigente?</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -26393,7 +27268,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>RMSE base exigente ×100</t>
+          <t>RMSE base más exigente ×100</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -26403,7 +27278,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>¿Bate?</t>
+          <t>¿Bate a la base más exigente?</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -26901,7 +27776,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>RMSE base exigente ×100</t>
+          <t>RMSE base más exigente ×100</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -26911,7 +27786,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>¿Bate?</t>
+          <t>¿Bate a la base más exigente?</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -27409,7 +28284,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>RMSE base exigente ×100</t>
+          <t>RMSE base más exigente ×100</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -27419,7 +28294,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>¿Bate?</t>
+          <t>¿Bate a la base más exigente?</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -27917,7 +28792,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>RMSE base exigente ×100</t>
+          <t>RMSE base más exigente ×100</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -27927,7 +28802,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>¿Bate?</t>
+          <t>¿Bate a la base más exigente?</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -28425,7 +29300,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>RMSE base exigente ×100</t>
+          <t>RMSE base más exigente ×100</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -28435,7 +29310,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>¿Bate?</t>
+          <t>¿Bate a la base más exigente?</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
